--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G399"/>
+  <dimension ref="A1:G400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11211,6 +11211,33 @@
       <c r="G399" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="C400" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="D400" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="E400" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="F400" t="n">
+        <v>347.49</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B418"/>
+  <dimension ref="A1:B419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15408,6 +15435,16 @@
       </c>
       <c r="B418" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -15576,28 +15613,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3022853555361286</v>
+        <v>-0.3013778634232341</v>
       </c>
       <c r="J2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2835657031140368</v>
+        <v>0.2832957927308791</v>
       </c>
       <c r="M2" t="n">
-        <v>2.777463360414074</v>
+        <v>2.774187848073933</v>
       </c>
       <c r="N2" t="n">
-        <v>12.66284596981743</v>
+        <v>12.63955044818569</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55848928195905</v>
+        <v>3.555214543200691</v>
       </c>
       <c r="P2" t="n">
-        <v>348.4194143620824</v>
+        <v>348.4100299852714</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15654,28 +15691,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.314872831117758</v>
+        <v>-0.3141024406611774</v>
       </c>
       <c r="J3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4539357393139083</v>
+        <v>0.4538170529470233</v>
       </c>
       <c r="M3" t="n">
-        <v>1.869198281500366</v>
+        <v>1.867804257255989</v>
       </c>
       <c r="N3" t="n">
-        <v>6.541753825544558</v>
+        <v>6.531441575531758</v>
       </c>
       <c r="O3" t="n">
-        <v>2.557685247551887</v>
+        <v>2.555668518319964</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2530525920403</v>
+        <v>344.2450859835889</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15732,28 +15769,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1120655365793871</v>
+        <v>-0.1116301206600529</v>
       </c>
       <c r="J4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0811992955140981</v>
+        <v>0.08099931851156128</v>
       </c>
       <c r="M4" t="n">
-        <v>2.088098110007786</v>
+        <v>2.085011575977086</v>
       </c>
       <c r="N4" t="n">
-        <v>7.794489038365027</v>
+        <v>7.776897159832672</v>
       </c>
       <c r="O4" t="n">
-        <v>2.79186121402283</v>
+        <v>2.788708869680138</v>
       </c>
       <c r="P4" t="n">
-        <v>350.3515545738831</v>
+        <v>350.347051937443</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15810,28 +15847,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004070463309259239</v>
+        <v>-0.005121355167684458</v>
       </c>
       <c r="J5" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000108145536318438</v>
+        <v>0.0001718705115617558</v>
       </c>
       <c r="M5" t="n">
-        <v>2.211361461581482</v>
+        <v>2.210622445819062</v>
       </c>
       <c r="N5" t="n">
-        <v>8.402462117520413</v>
+        <v>8.392722648917674</v>
       </c>
       <c r="O5" t="n">
-        <v>2.898700073743472</v>
+        <v>2.897019614865884</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7016131002292</v>
+        <v>342.7124803739465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15888,28 +15925,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2754853640109934</v>
+        <v>-0.2734098106821773</v>
       </c>
       <c r="J6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K6" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3147715637881435</v>
+        <v>0.3116211580483299</v>
       </c>
       <c r="M6" t="n">
-        <v>2.449802432595035</v>
+        <v>2.456169504696746</v>
       </c>
       <c r="N6" t="n">
-        <v>9.061735667146305</v>
+        <v>9.083178809245963</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010271693244034</v>
+        <v>3.013831250957154</v>
       </c>
       <c r="P6" t="n">
-        <v>350.5072572356845</v>
+        <v>350.4857939367178</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15947,7 +15984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G399"/>
+  <dimension ref="A1:G400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30713,6 +30750,43 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-42.87146661696978,173.310316081465</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-42.87210372493791,173.3100733511485</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-42.87276723747299,173.31005373427416</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-42.87342586020202,173.30995538594578</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-42.87407877989885,173.3100973353448</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G400"/>
+  <dimension ref="A1:G402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11238,6 +11238,60 @@
       <c r="G400" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="C401" t="n">
+        <v>337.83</v>
+      </c>
+      <c r="D401" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="E401" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="F401" t="n">
+        <v>347.13</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="C402" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="D402" t="n">
+        <v>347.45</v>
+      </c>
+      <c r="E402" t="n">
+        <v>340.59</v>
+      </c>
+      <c r="F402" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B419"/>
+  <dimension ref="A1:B421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15445,6 +15499,26 @@
       </c>
       <c r="B419" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -15613,28 +15687,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3013778634232341</v>
+        <v>-0.299403638044617</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2832957927308791</v>
+        <v>0.2824749765304571</v>
       </c>
       <c r="M2" t="n">
-        <v>2.774187848073933</v>
+        <v>2.768270372217545</v>
       </c>
       <c r="N2" t="n">
-        <v>12.63955044818569</v>
+        <v>12.59681069978078</v>
       </c>
       <c r="O2" t="n">
-        <v>3.555214543200691</v>
+        <v>3.549198599653276</v>
       </c>
       <c r="P2" t="n">
-        <v>348.4100299852714</v>
+        <v>348.3895313424108</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15691,28 +15765,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3141024406611774</v>
+        <v>-0.3120778524630225</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4538170529470233</v>
+        <v>0.4524560291132317</v>
       </c>
       <c r="M3" t="n">
-        <v>1.867804257255989</v>
+        <v>1.867094932946437</v>
       </c>
       <c r="N3" t="n">
-        <v>6.531441575531758</v>
+        <v>6.520154779720916</v>
       </c>
       <c r="O3" t="n">
-        <v>2.555668518319964</v>
+        <v>2.553459374989333</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2450859835889</v>
+        <v>344.2240646834472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15769,28 +15843,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1116301206600529</v>
+        <v>-0.1114893630775361</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08099931851156128</v>
+        <v>0.08160939765332498</v>
       </c>
       <c r="M4" t="n">
-        <v>2.085011575977086</v>
+        <v>2.075298686404312</v>
       </c>
       <c r="N4" t="n">
-        <v>7.776897159832672</v>
+        <v>7.738263496423916</v>
       </c>
       <c r="O4" t="n">
-        <v>2.788708869680138</v>
+        <v>2.78177344448176</v>
       </c>
       <c r="P4" t="n">
-        <v>350.347051937443</v>
+        <v>350.3455916317457</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15847,28 +15921,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005121355167684458</v>
+        <v>-0.007128952149645497</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001718705115617558</v>
+        <v>0.0003357274525001008</v>
       </c>
       <c r="M5" t="n">
-        <v>2.210622445819062</v>
+        <v>2.208755112791236</v>
       </c>
       <c r="N5" t="n">
-        <v>8.392722648917674</v>
+        <v>8.371592912835762</v>
       </c>
       <c r="O5" t="n">
-        <v>2.897019614865884</v>
+        <v>2.893370510811874</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7124803739465</v>
+        <v>342.7333224028817</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15925,28 +15999,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2734098106821773</v>
+        <v>-0.26966766092018</v>
       </c>
       <c r="J6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3116211580483299</v>
+        <v>0.3063304013933764</v>
       </c>
       <c r="M6" t="n">
-        <v>2.456169504696746</v>
+        <v>2.466209872550241</v>
       </c>
       <c r="N6" t="n">
-        <v>9.083178809245963</v>
+        <v>9.10981764860821</v>
       </c>
       <c r="O6" t="n">
-        <v>3.013831250957154</v>
+        <v>3.018247446550433</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4857939367178</v>
+        <v>350.4469433817408</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15984,7 +16058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G400"/>
+  <dimension ref="A1:G402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30787,6 +30861,80 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-42.87146648878197,173.31031524235559</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-42.87210417117562,173.31007660066834</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-42.872766764899744,173.31004592491425</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-42.87342586020202,173.30995538594578</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-42.874078990137065,173.31009293692276</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:07:44+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-42.87146734947138,173.3103208763762</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-42.87210488185035,173.3100817758297</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-42.872766609836546,173.310043362468</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-42.87342582231157,173.30995697676468</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-42.8740790076569,173.31009257038758</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G402"/>
+  <dimension ref="A1:G403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11292,6 +11292,33 @@
       <c r="G402" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="C403" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="D403" t="n">
+        <v>347.83</v>
+      </c>
+      <c r="E403" t="n">
+        <v>341.21</v>
+      </c>
+      <c r="F403" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15519,6 +15546,16 @@
       </c>
       <c r="B421" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -15687,28 +15724,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.299403638044617</v>
+        <v>-0.2978426338765292</v>
       </c>
       <c r="J2" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2824749765304571</v>
+        <v>0.2810507307212347</v>
       </c>
       <c r="M2" t="n">
-        <v>2.768270372217545</v>
+        <v>2.767671433643979</v>
       </c>
       <c r="N2" t="n">
-        <v>12.59681069978078</v>
+        <v>12.59043701326318</v>
       </c>
       <c r="O2" t="n">
-        <v>3.549198599653276</v>
+        <v>3.548300581019481</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3895313424108</v>
+        <v>348.3732297806815</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15765,28 +15802,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3120778524630225</v>
+        <v>-0.3106602677563668</v>
       </c>
       <c r="J3" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4524560291132317</v>
+        <v>0.4507560797107996</v>
       </c>
       <c r="M3" t="n">
-        <v>1.867094932946437</v>
+        <v>1.868448933289762</v>
       </c>
       <c r="N3" t="n">
-        <v>6.520154779720916</v>
+        <v>6.524521084836226</v>
       </c>
       <c r="O3" t="n">
-        <v>2.553459374989333</v>
+        <v>2.554314210279586</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2240646834472</v>
+        <v>344.2092608507129</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15843,28 +15880,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1114893630775361</v>
+        <v>-0.1112737565581199</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08160939765332498</v>
+        <v>0.08171951476209993</v>
       </c>
       <c r="M4" t="n">
-        <v>2.075298686404312</v>
+        <v>2.071171114532248</v>
       </c>
       <c r="N4" t="n">
-        <v>7.738263496423916</v>
+        <v>7.719490284505524</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78177344448176</v>
+        <v>2.778397071065531</v>
       </c>
       <c r="P4" t="n">
-        <v>350.3455916317457</v>
+        <v>350.3433400535262</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15921,28 +15958,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007128952149645497</v>
+        <v>-0.007782604814607284</v>
       </c>
       <c r="J5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003357274525001008</v>
+        <v>0.0004020451984195761</v>
       </c>
       <c r="M5" t="n">
-        <v>2.208755112791236</v>
+        <v>2.206229858511195</v>
       </c>
       <c r="N5" t="n">
-        <v>8.371592912835762</v>
+        <v>8.35514488275113</v>
       </c>
       <c r="O5" t="n">
-        <v>2.893370510811874</v>
+        <v>2.890526748319608</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7333224028817</v>
+        <v>342.7401484956528</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15999,28 +16036,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.26966766092018</v>
+        <v>-0.2680920218802697</v>
       </c>
       <c r="J6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3063304013933764</v>
+        <v>0.3043973206015793</v>
       </c>
       <c r="M6" t="n">
-        <v>2.466209872550241</v>
+        <v>2.469434942601139</v>
       </c>
       <c r="N6" t="n">
-        <v>9.10981764860821</v>
+        <v>9.112588314021409</v>
       </c>
       <c r="O6" t="n">
-        <v>3.018247446550433</v>
+        <v>3.018706397452625</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4469433817408</v>
+        <v>350.43048898809</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16058,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G402"/>
+  <dimension ref="A1:G403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30935,6 +30972,43 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-42.8714690342243,173.31033190467235</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-42.87210587348908,173.31008899698526</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-42.872766890427066,173.31004799927547</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-42.87342564160295,173.30996456374712</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-42.874079346373655,173.31008548404088</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G403"/>
+  <dimension ref="A1:G405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11317,6 +11317,60 @@
         <v>346.52</v>
       </c>
       <c r="G403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="C404" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="D404" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="E404" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="F404" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>344</v>
+      </c>
+      <c r="C405" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="D405" t="n">
+        <v>346.67</v>
+      </c>
+      <c r="E405" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="F405" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="G405" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11333,7 +11387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B422"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15556,6 +15610,26 @@
       </c>
       <c r="B422" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -15724,28 +15798,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2978426338765292</v>
+        <v>-0.2944988548608373</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2810507307212347</v>
+        <v>0.277746846869625</v>
       </c>
       <c r="M2" t="n">
-        <v>2.767671433643979</v>
+        <v>2.767823507204644</v>
       </c>
       <c r="N2" t="n">
-        <v>12.59043701326318</v>
+        <v>12.5857976379663</v>
       </c>
       <c r="O2" t="n">
-        <v>3.548300581019481</v>
+        <v>3.54764677468971</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3732297806815</v>
+        <v>348.3382086720334</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15802,28 +15876,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3106602677563668</v>
+        <v>-0.3082992773407739</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4507560797107996</v>
+        <v>0.4485467145777932</v>
       </c>
       <c r="M3" t="n">
-        <v>1.868448933289762</v>
+        <v>1.869236911441243</v>
       </c>
       <c r="N3" t="n">
-        <v>6.524521084836226</v>
+        <v>6.521076222680287</v>
       </c>
       <c r="O3" t="n">
-        <v>2.554314210279586</v>
+        <v>2.553639798930203</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2092608507129</v>
+        <v>344.1845321102097</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15880,28 +15954,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1112737565581199</v>
+        <v>-0.1120119256708674</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08171951476209993</v>
+        <v>0.08350972054671602</v>
       </c>
       <c r="M4" t="n">
-        <v>2.071171114532248</v>
+        <v>2.064813700622983</v>
       </c>
       <c r="N4" t="n">
-        <v>7.719490284505524</v>
+        <v>7.684092326213666</v>
       </c>
       <c r="O4" t="n">
-        <v>2.778397071065531</v>
+        <v>2.772019539291465</v>
       </c>
       <c r="P4" t="n">
-        <v>350.3433400535262</v>
+        <v>350.3510706956331</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15958,28 +16032,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.007782604814607284</v>
+        <v>-0.008982044617544038</v>
       </c>
       <c r="J5" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004020451984195761</v>
+        <v>0.0005406864906956077</v>
       </c>
       <c r="M5" t="n">
-        <v>2.206229858511195</v>
+        <v>2.200746306532239</v>
       </c>
       <c r="N5" t="n">
-        <v>8.35514488275113</v>
+        <v>8.322297399892934</v>
       </c>
       <c r="O5" t="n">
-        <v>2.890526748319608</v>
+        <v>2.884839232937069</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7401484956528</v>
+        <v>342.7527058765441</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16036,28 +16110,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2680920218802697</v>
+        <v>-0.2650560612161206</v>
       </c>
       <c r="J6" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K6" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3043973206015793</v>
+        <v>0.3007588769849722</v>
       </c>
       <c r="M6" t="n">
-        <v>2.469434942601139</v>
+        <v>2.47523777158351</v>
       </c>
       <c r="N6" t="n">
-        <v>9.112588314021409</v>
+        <v>9.115011096013346</v>
       </c>
       <c r="O6" t="n">
-        <v>3.018706397452625</v>
+        <v>3.019107665521941</v>
       </c>
       <c r="P6" t="n">
-        <v>350.43048898809</v>
+        <v>350.3986930157193</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16095,7 +16169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G403"/>
+  <dimension ref="A1:G405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31009,6 +31083,80 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-42.871469345537236,173.31033394250977</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-42.872104865323024,173.3100816554771</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-42.87276598219918,173.3100329906621</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-42.8734257523599,173.30995991366112</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-42.874079369733415,173.3100849953273</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-42.87146967516263,173.31033610021998</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-42.87210536114247,173.31008526605487</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-42.87276603388699,173.31003384481082</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-42.87342547838185,173.30997141650545</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-42.874079416452915,173.31008401790015</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G405"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11371,6 +11371,87 @@
         <v>346.4</v>
       </c>
       <c r="G405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>344</v>
+      </c>
+      <c r="C406" t="n">
+        <v>338.17</v>
+      </c>
+      <c r="D406" t="n">
+        <v>346.06</v>
+      </c>
+      <c r="E406" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="F406" t="n">
+        <v>345.04</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>343.14</v>
+      </c>
+      <c r="C407" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="D407" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="E407" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="F407" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>342.24</v>
+      </c>
+      <c r="C408" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="D408" t="n">
+        <v>344.94</v>
+      </c>
+      <c r="E408" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="F408" t="n">
+        <v>343.47</v>
+      </c>
+      <c r="G408" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11387,7 +11468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15630,6 +15711,36 @@
       </c>
       <c r="B424" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -15798,28 +15909,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2944988548608373</v>
+        <v>-0.2907300003240485</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.277746846869625</v>
+        <v>0.2749403984898934</v>
       </c>
       <c r="M2" t="n">
-        <v>2.767823507204644</v>
+        <v>2.763280529574002</v>
       </c>
       <c r="N2" t="n">
-        <v>12.5857976379663</v>
+        <v>12.54639518543482</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54764677468971</v>
+        <v>3.542089099025436</v>
       </c>
       <c r="P2" t="n">
-        <v>348.3382086720334</v>
+        <v>348.2985929021153</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15876,28 +15987,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3082992773407739</v>
+        <v>-0.3059742963212818</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4485467145777932</v>
+        <v>0.4479900921223459</v>
       </c>
       <c r="M3" t="n">
-        <v>1.869236911441243</v>
+        <v>1.86530569395438</v>
       </c>
       <c r="N3" t="n">
-        <v>6.521076222680287</v>
+        <v>6.493105630386063</v>
       </c>
       <c r="O3" t="n">
-        <v>2.553639798930203</v>
+        <v>2.54815730095025</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1845321102097</v>
+        <v>344.1600927581341</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15954,28 +16065,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1120119256708674</v>
+        <v>-0.1146727729331542</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08350972054671602</v>
+        <v>0.08817856700964821</v>
       </c>
       <c r="M4" t="n">
-        <v>2.064813700622983</v>
+        <v>2.063729912013718</v>
       </c>
       <c r="N4" t="n">
-        <v>7.684092326213666</v>
+        <v>7.653701200583829</v>
       </c>
       <c r="O4" t="n">
-        <v>2.772019539291465</v>
+        <v>2.766532342226244</v>
       </c>
       <c r="P4" t="n">
-        <v>350.3510706956331</v>
+        <v>350.3790513258535</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16032,28 +16143,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008982044617544038</v>
+        <v>-0.01246952734920027</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005406864906956077</v>
+        <v>0.00105265597544979</v>
       </c>
       <c r="M5" t="n">
-        <v>2.200746306532239</v>
+        <v>2.200195666525014</v>
       </c>
       <c r="N5" t="n">
-        <v>8.322297399892934</v>
+        <v>8.30539392042375</v>
       </c>
       <c r="O5" t="n">
-        <v>2.884839232937069</v>
+        <v>2.881908034692251</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7527058765441</v>
+        <v>342.789378201437</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16110,28 +16221,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2650560612161206</v>
+        <v>-0.2639372079692142</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3007588769849722</v>
+        <v>0.3021665634095226</v>
       </c>
       <c r="M6" t="n">
-        <v>2.47523777158351</v>
+        <v>2.463582612264299</v>
       </c>
       <c r="N6" t="n">
-        <v>9.115011096013346</v>
+        <v>9.055464262881062</v>
       </c>
       <c r="O6" t="n">
-        <v>3.019107665521941</v>
+        <v>3.00922984547227</v>
       </c>
       <c r="P6" t="n">
-        <v>350.3986930157193</v>
+        <v>350.3869374894639</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16169,7 +16280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G405"/>
+  <dimension ref="A1:G408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31157,6 +31268,117 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-42.87146967516263,173.31033610021998</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-42.87210473310449,173.31008069265638</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-42.87276558346436,173.3100264015149</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-42.87342578150644,173.3099586899543</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-42.87408021068333,173.31006740163852</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-42.87146810028531,173.3103257911603</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-42.872103493555336,173.3100716662123</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-42.872765214265094,173.31002030045278</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-42.87342597387324,173.30995061348906</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-42.87408089979308,173.31005298458766</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-42.87146645215688,173.31031500261003</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-42.872103146481436,173.31006913880802</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-42.87276475645757,173.3100127351358</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-42.873426151666294,173.3099431488772</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-42.87408112754928,173.3100482196301</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11452,6 +11452,60 @@
         <v>343.47</v>
       </c>
       <c r="G408" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>342.13</v>
+      </c>
+      <c r="C409" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="D409" t="n">
+        <v>345.08</v>
+      </c>
+      <c r="E409" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="F409" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="C410" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="D410" t="n">
+        <v>344.36</v>
+      </c>
+      <c r="E410" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>341.85</v>
+      </c>
+      <c r="G410" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11468,7 +11522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15741,6 +15795,26 @@
       </c>
       <c r="B427" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -15909,28 +15983,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2907300003240485</v>
+        <v>-0.2894011615865194</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2749403984898934</v>
+        <v>0.2750523702144988</v>
       </c>
       <c r="M2" t="n">
-        <v>2.763280529574002</v>
+        <v>2.755477714821181</v>
       </c>
       <c r="N2" t="n">
-        <v>12.54639518543482</v>
+        <v>12.49466891234702</v>
       </c>
       <c r="O2" t="n">
-        <v>3.542089099025436</v>
+        <v>3.534779895884187</v>
       </c>
       <c r="P2" t="n">
-        <v>348.2985929021153</v>
+        <v>348.2845889530083</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15987,28 +16061,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3059742963212818</v>
+        <v>-0.3048903992751841</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4479900921223459</v>
+        <v>0.4485870939277327</v>
       </c>
       <c r="M3" t="n">
-        <v>1.86530569395438</v>
+        <v>1.860778862238384</v>
       </c>
       <c r="N3" t="n">
-        <v>6.493105630386063</v>
+        <v>6.467711216626506</v>
       </c>
       <c r="O3" t="n">
-        <v>2.54815730095025</v>
+        <v>2.543169521802765</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1600927581341</v>
+        <v>344.1486699337544</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16065,28 +16139,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1146727729331542</v>
+        <v>-0.1171398938767473</v>
       </c>
       <c r="J4" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08817856700964821</v>
+        <v>0.09217423127664304</v>
       </c>
       <c r="M4" t="n">
-        <v>2.063729912013718</v>
+        <v>2.066974759535717</v>
       </c>
       <c r="N4" t="n">
-        <v>7.653701200583829</v>
+        <v>7.649545010273744</v>
       </c>
       <c r="O4" t="n">
-        <v>2.766532342226244</v>
+        <v>2.765781085023495</v>
       </c>
       <c r="P4" t="n">
-        <v>350.3790513258535</v>
+        <v>350.4050543722274</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16143,28 +16217,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01246952734920027</v>
+        <v>-0.01561389474717097</v>
       </c>
       <c r="J5" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K5" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00105265597544979</v>
+        <v>0.001656245196790529</v>
       </c>
       <c r="M5" t="n">
-        <v>2.200195666525014</v>
+        <v>2.203676376622643</v>
       </c>
       <c r="N5" t="n">
-        <v>8.30539392042375</v>
+        <v>8.317847214567818</v>
       </c>
       <c r="O5" t="n">
-        <v>2.881908034692251</v>
+        <v>2.884067824196896</v>
       </c>
       <c r="P5" t="n">
-        <v>342.789378201437</v>
+        <v>342.8225167914609</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16221,28 +16295,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2639372079692142</v>
+        <v>-0.2651005443058311</v>
       </c>
       <c r="J6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3021665634095226</v>
+        <v>0.3060702970338687</v>
       </c>
       <c r="M6" t="n">
-        <v>2.463582612264299</v>
+        <v>2.45657799721625</v>
       </c>
       <c r="N6" t="n">
-        <v>9.055464262881062</v>
+        <v>9.018794710162009</v>
       </c>
       <c r="O6" t="n">
-        <v>3.00922984547227</v>
+        <v>3.003130818023419</v>
       </c>
       <c r="P6" t="n">
-        <v>350.3869374894639</v>
+        <v>350.3991993532907</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16280,7 +16354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G408"/>
+  <dimension ref="A1:G410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31379,6 +31453,80 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-42.871466250718896,173.31031368400946</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-42.872103212590766,173.31006962021834</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-42.87276485983351,173.31001444343318</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-42.87342626242237,173.30993849879115</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-42.87408175825774,173.31003502436278</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-42.87146559146719,173.31030936858954</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-42.87210286551683,173.3100670928141</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-42.87276432818558,173.31000565790393</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-42.87342622744678,173.3099399672394</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-42.87408207361139,173.31002842672905</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0408/nzd0408.xlsx
+++ b/data/nzd0408/nzd0408.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G410"/>
+  <dimension ref="A1:G411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11506,6 +11506,33 @@
         <v>341.85</v>
       </c>
       <c r="G410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="C411" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="D411" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="E411" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="F411" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="G411" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11522,7 +11549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B429"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15815,6 +15842,16 @@
       </c>
       <c r="B429" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -15983,28 +16020,28 @@
         <v>0.1554</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2894011615865194</v>
+        <v>-0.2890495839342771</v>
       </c>
       <c r="J2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K2" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2750523702144988</v>
+        <v>0.2755957651009789</v>
       </c>
       <c r="M2" t="n">
-        <v>2.755477714821181</v>
+        <v>2.750258034750566</v>
       </c>
       <c r="N2" t="n">
-        <v>12.49466891234702</v>
+        <v>12.46552412965384</v>
       </c>
       <c r="O2" t="n">
-        <v>3.534779895884187</v>
+        <v>3.530654915118984</v>
       </c>
       <c r="P2" t="n">
-        <v>348.2845889530083</v>
+        <v>348.2808674654689</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16061,28 +16098,28 @@
         <v>0.1664</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3048903992751841</v>
+        <v>-0.3044898675955911</v>
       </c>
       <c r="J3" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K3" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4485870939277327</v>
+        <v>0.4491721019515247</v>
       </c>
       <c r="M3" t="n">
-        <v>1.860778862238384</v>
+        <v>1.857917964090449</v>
       </c>
       <c r="N3" t="n">
-        <v>6.467711216626506</v>
+        <v>6.45366250377472</v>
       </c>
       <c r="O3" t="n">
-        <v>2.543169521802765</v>
+        <v>2.540405972236469</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1486699337544</v>
+        <v>344.1444302625319</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16139,28 +16176,28 @@
         <v>0.1319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1171398938767473</v>
+        <v>-0.1194081027123192</v>
       </c>
       <c r="J4" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K4" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09217423127664304</v>
+        <v>0.09526475314882898</v>
       </c>
       <c r="M4" t="n">
-        <v>2.066974759535717</v>
+        <v>2.074121044912338</v>
       </c>
       <c r="N4" t="n">
-        <v>7.649545010273744</v>
+        <v>7.686245733812839</v>
       </c>
       <c r="O4" t="n">
-        <v>2.765781085023495</v>
+        <v>2.772407930628687</v>
       </c>
       <c r="P4" t="n">
-        <v>350.4050543722274</v>
+        <v>350.429063608492</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16217,28 +16254,28 @@
         <v>0.1256</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01561389474717097</v>
+        <v>-0.01787318380629142</v>
       </c>
       <c r="J5" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K5" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001656245196790529</v>
+        <v>0.002166226316414943</v>
       </c>
       <c r="M5" t="n">
-        <v>2.203676376622643</v>
+        <v>2.208712313376867</v>
       </c>
       <c r="N5" t="n">
-        <v>8.317847214567818</v>
+        <v>8.352483394769067</v>
       </c>
       <c r="O5" t="n">
-        <v>2.884067824196896</v>
+        <v>2.890066330513725</v>
       </c>
       <c r="P5" t="n">
-        <v>342.8225167914609</v>
+        <v>342.8464316109254</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16295,28 +16332,28 @@
         <v>0.1241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2651005443058311</v>
+        <v>-0.2660521474091023</v>
       </c>
       <c r="J6" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3060702970338687</v>
+        <v>0.3084852190000253</v>
       </c>
       <c r="M6" t="n">
-        <v>2.45657799721625</v>
+        <v>2.454660790232215</v>
       </c>
       <c r="N6" t="n">
-        <v>9.018794710162009</v>
+        <v>9.006541423725572</v>
       </c>
       <c r="O6" t="n">
-        <v>3.003130818023419</v>
+        <v>3.001090039256665</v>
       </c>
       <c r="P6" t="n">
-        <v>350.3991993532907</v>
+        <v>350.4092721752365</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16354,7 +16391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G410"/>
+  <dimension ref="A1:G411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31527,6 +31564,43 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-42.87146469415211,173.31030349482367</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-42.87210251844283,173.31006456540985</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-42.87276294737459,173.3099828399328</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-42.8734266821279,173.30992087741214</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-42.87408239480455,173.31002170691679</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
